--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Algarpredio\Downloads\Recibos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8ED1532-A6AE-4319-B2A7-B28C85D774B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9EF5C9-977F-4606-ADBE-3A37A9B3AD66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,6 @@
     <sheet name="Saramago_2024_Convertido" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -13706,7 +13705,7 @@
         <v>1</v>
       </c>
       <c r="X162" t="str">
-        <f t="shared" ref="X162:X193" si="38">IF(A162="The View","Projeto",IF(W162&gt;=0.85,"A · Premium ativo",IF(W162&gt;=0.55,"B · Benchmark local","C · Histórico/secundário")))</f>
+        <f t="shared" ref="X162:X173" si="38">IF(A162="The View","Projeto",IF(W162&gt;=0.85,"A · Premium ativo",IF(W162&gt;=0.55,"B · Benchmark local","C · Histórico/secundário")))</f>
         <v>A · Premium ativo</v>
       </c>
       <c r="Y162" t="str">
@@ -14675,7 +14674,7 @@
         <v>535500</v>
       </c>
       <c r="J176" s="1">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="K176" s="6">
         <v>4410.441044104411</v>
@@ -18253,7 +18252,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>219</v>
       </c>
